--- a/ITX.MC.xlsx
+++ b/ITX.MC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44902949-7F23-47D1-BAE4-BEFA13CD59F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF594752-B9D4-46B6-B691-E1410E3EFBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{D8A593F9-CE2E-4D8C-B815-D7E0264BAFFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -764,13 +764,19 @@
     <numFmt numFmtId="172" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="173" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1127,140 +1133,143 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="11" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1336,16 +1345,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>14288</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>20638</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15876</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1360,7 +1369,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10215563" y="266700"/>
+          <a:off x="10820401" y="219075"/>
           <a:ext cx="6350" cy="19443700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1748,8 +1757,8 @@
       <c r="I3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="75">
-        <v>55</v>
+      <c r="J3" s="87">
+        <v>54.85</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1766,10 +1775,10 @@
         <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>3116.1155050000002</v>
-      </c>
-      <c r="K4" s="84" t="s">
-        <v>207</v>
+        <v>3115.9215389999999</v>
+      </c>
+      <c r="K4" s="88" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1787,7 +1796,7 @@
       </c>
       <c r="J5" s="5">
         <f>J4*J3</f>
-        <v>171386.35277500001</v>
+        <v>170908.29641415001</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1795,11 +1804,11 @@
         <v>4</v>
       </c>
       <c r="J6" s="5">
-        <f>5045+5752</f>
-        <v>10797</v>
-      </c>
-      <c r="K6" s="84" t="s">
-        <v>207</v>
+        <f>6038+4361</f>
+        <v>10399</v>
+      </c>
+      <c r="K6" s="88" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1823,10 +1832,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="84" t="s">
-        <v>207</v>
+        <v>1</v>
+      </c>
+      <c r="K7" s="88" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1846,7 +1855,7 @@
       </c>
       <c r="J8" s="5">
         <f>J5-J6+J7</f>
-        <v>160589.35277500001</v>
+        <v>160510.29641415001</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1928,12 +1937,12 @@
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="78" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2030,16 +2039,16 @@
       <c r="N2" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="O2" s="84" t="s">
+      <c r="O2" s="79" t="s">
         <v>207</v>
       </c>
-      <c r="P2" s="84" t="s">
+      <c r="P2" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="Q2" s="84" t="s">
+      <c r="Q2" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="R2" s="84" t="s">
+      <c r="R2" s="79" t="s">
         <v>210</v>
       </c>
       <c r="S2" s="2"/>
@@ -2092,203 +2101,222 @@
       </c>
       <c r="AF2" s="20"/>
     </row>
-    <row r="3" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="81">
         <f>1588+203+407</f>
         <v>2198</v>
       </c>
-      <c r="L3" s="86">
+      <c r="L3" s="81">
         <f>1534+379+210</f>
         <v>2123</v>
       </c>
-      <c r="M3" s="87">
+      <c r="M3" s="82">
         <f>1528+380+213</f>
         <v>2121</v>
       </c>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87">
+      <c r="N3" s="82"/>
+      <c r="O3" s="82">
         <f>1495+376+217</f>
         <v>2088</v>
       </c>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
-      <c r="Z3" s="86">
+      <c r="P3" s="82">
+        <f>1487+374+223</f>
+        <v>2084</v>
+      </c>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="Z3" s="81">
         <f>1550+391+209</f>
         <v>2150</v>
       </c>
-      <c r="AA3" s="86">
+      <c r="AA3" s="81">
         <f>1500+374+215</f>
         <v>2089</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="74" t="s">
         <v>196</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="81">
         <v>812</v>
       </c>
-      <c r="L4" s="86">
+      <c r="L4" s="81">
         <v>801</v>
       </c>
-      <c r="M4" s="87">
+      <c r="M4" s="82">
         <v>800</v>
       </c>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87">
+      <c r="N4" s="82"/>
+      <c r="O4" s="82">
         <v>792</v>
       </c>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="Z4" s="86">
+      <c r="P4" s="82">
+        <v>789</v>
+      </c>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="Z4" s="81">
         <v>800</v>
       </c>
-      <c r="AA4" s="86">
+      <c r="AA4" s="81">
         <v>791</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="81">
         <v>542</v>
       </c>
-      <c r="L5" s="86">
+      <c r="L5" s="81">
         <v>518</v>
       </c>
-      <c r="M5" s="87">
+      <c r="M5" s="82">
         <v>519</v>
       </c>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87">
+      <c r="N5" s="82"/>
+      <c r="O5" s="82">
         <v>509</v>
       </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="Z5" s="86">
+      <c r="P5" s="82">
+        <v>509</v>
+      </c>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="Z5" s="81">
         <v>528</v>
       </c>
-      <c r="AA5" s="86">
+      <c r="AA5" s="81">
         <v>511</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="81">
         <v>855</v>
       </c>
-      <c r="L6" s="86">
+      <c r="L6" s="81">
         <v>856</v>
       </c>
-      <c r="M6" s="87">
+      <c r="M6" s="82">
         <v>859</v>
       </c>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87">
+      <c r="N6" s="82"/>
+      <c r="O6" s="82">
         <v>851</v>
       </c>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="87"/>
-      <c r="R6" s="87"/>
-      <c r="Z6" s="86">
+      <c r="P6" s="82">
+        <v>849</v>
+      </c>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="Z6" s="81">
         <v>854</v>
       </c>
-      <c r="AA6" s="86">
+      <c r="AA6" s="81">
         <v>852</v>
       </c>
     </row>
-    <row r="7" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="74" t="s">
         <v>199</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="81">
         <v>845</v>
       </c>
-      <c r="L7" s="86">
+      <c r="L7" s="81">
         <v>839</v>
       </c>
-      <c r="M7" s="87">
+      <c r="M7" s="82">
         <v>839</v>
       </c>
-      <c r="N7" s="87"/>
-      <c r="O7" s="87">
+      <c r="N7" s="82"/>
+      <c r="O7" s="82">
         <v>837</v>
       </c>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="87"/>
-      <c r="Z7" s="86">
+      <c r="P7" s="82">
         <v>835</v>
       </c>
-      <c r="AA7" s="86">
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="Z7" s="81">
+        <v>835</v>
+      </c>
+      <c r="AA7" s="81">
         <v>834</v>
       </c>
     </row>
-    <row r="8" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="81">
         <v>407</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="81">
         <v>391</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="82">
         <v>389</v>
       </c>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87">
+      <c r="N8" s="82"/>
+      <c r="O8" s="82">
         <v>379</v>
       </c>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="Z8" s="86">
+      <c r="P8" s="82">
+        <v>378</v>
+      </c>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="Z8" s="81">
         <v>396</v>
       </c>
-      <c r="AA8" s="86">
+      <c r="AA8" s="81">
         <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:33" s="86" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" s="81" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="81">
         <v>203</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="81">
         <v>0</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="82">
         <v>0</v>
       </c>
-      <c r="N9" s="87"/>
-      <c r="O9" s="87"/>
-      <c r="P9" s="87"/>
-      <c r="Q9" s="87"/>
-      <c r="R9" s="87"/>
-      <c r="Z9" s="86">
+      <c r="N9" s="82">
         <v>0</v>
       </c>
-      <c r="AA9" s="86">
+      <c r="O9" s="82">
+        <v>0</v>
+      </c>
+      <c r="P9" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="Z9" s="81">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="81">
         <v>0</v>
       </c>
     </row>
@@ -2332,10 +2360,13 @@
         <v>0</v>
       </c>
       <c r="O10" s="28">
-        <f t="shared" si="1"/>
+        <f>+SUM(O3:O9)</f>
         <v>5456</v>
       </c>
-      <c r="P10" s="28"/>
+      <c r="P10" s="28">
+        <f>+SUM(P3:P9)</f>
+        <v>5444</v>
+      </c>
       <c r="Q10" s="28"/>
       <c r="R10" s="28"/>
       <c r="S10" s="28"/>
@@ -3442,7 +3473,10 @@
       <c r="O29" s="28">
         <v>8750</v>
       </c>
-      <c r="P29" s="28"/>
+      <c r="P29" s="28">
+        <f>19755-O29</f>
+        <v>11005</v>
+      </c>
       <c r="Q29" s="28"/>
       <c r="R29" s="28"/>
       <c r="S29" s="21"/>
@@ -3536,16 +3570,19 @@
         <f>11361-SUM(K30:L30)</f>
         <v>3707</v>
       </c>
-      <c r="N30" s="78">
+      <c r="N30" s="77">
         <f>+AA30-SUM(K30:M30)</f>
         <v>5281</v>
       </c>
-      <c r="O30" s="78">
+      <c r="O30" s="77">
         <v>3391</v>
       </c>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
-      <c r="R30" s="78"/>
+      <c r="P30" s="77">
+        <f>8159-O30</f>
+        <v>4768</v>
+      </c>
+      <c r="Q30" s="77"/>
+      <c r="R30" s="77"/>
       <c r="S30" s="21"/>
       <c r="T30" s="21">
         <v>11329</v>
@@ -3615,7 +3652,7 @@
         <v>6053</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" ref="K31:O31" si="16">K29-K30</f>
+        <f t="shared" ref="K31:P31" si="16">K29-K30</f>
         <v>5012</v>
       </c>
       <c r="L31" s="21">
@@ -3634,7 +3671,10 @@
         <f t="shared" si="16"/>
         <v>5359</v>
       </c>
-      <c r="P31" s="21"/>
+      <c r="P31" s="21">
+        <f t="shared" si="16"/>
+        <v>6237</v>
+      </c>
       <c r="Q31" s="21"/>
       <c r="R31" s="21"/>
       <c r="S31" s="21"/>
@@ -3718,16 +3758,19 @@
         <f>8479-SUM(K32:L32)</f>
         <v>2895</v>
       </c>
-      <c r="N32" s="78">
+      <c r="N32" s="77">
         <f>+AA32-SUM(K32:M32)</f>
         <v>3399</v>
       </c>
-      <c r="O32" s="78">
+      <c r="O32" s="77">
         <v>2779</v>
       </c>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
-      <c r="R32" s="78"/>
+      <c r="P32" s="77">
+        <f>6048-O32</f>
+        <v>3269</v>
+      </c>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="77"/>
       <c r="S32" s="21"/>
       <c r="T32" s="21">
         <v>9329</v>
@@ -3801,16 +3844,19 @@
         <f>-29-SUM(K33:L33)</f>
         <v>-24</v>
       </c>
-      <c r="N33" s="78">
+      <c r="N33" s="77">
         <f>+AA33-SUM(K33:M33)</f>
         <v>-48</v>
       </c>
-      <c r="O33" s="78">
+      <c r="O33" s="77">
         <v>-12</v>
       </c>
-      <c r="P33" s="78"/>
-      <c r="Q33" s="78"/>
-      <c r="R33" s="78"/>
+      <c r="P33" s="77">
+        <f>-35-O33</f>
+        <v>-23</v>
+      </c>
+      <c r="Q33" s="77"/>
+      <c r="R33" s="77"/>
       <c r="S33" s="21"/>
       <c r="T33" s="21">
         <v>-30</v>
@@ -3880,7 +3926,7 @@
         <v>2762</v>
       </c>
       <c r="K34" s="21">
-        <f t="shared" ref="K34:O34" si="19">K31-K32+K33</f>
+        <f t="shared" ref="K34:P34" si="19">K31-K32+K33</f>
         <v>2394</v>
       </c>
       <c r="L34" s="21">
@@ -3899,7 +3945,10 @@
         <f t="shared" si="19"/>
         <v>2568</v>
       </c>
-      <c r="P34" s="21"/>
+      <c r="P34" s="21">
+        <f t="shared" si="19"/>
+        <v>2945</v>
+      </c>
       <c r="Q34" s="21"/>
       <c r="R34" s="21"/>
       <c r="S34" s="21"/>
@@ -3979,16 +4028,18 @@
       <c r="M35" s="21">
         <v>0</v>
       </c>
-      <c r="N35" s="78">
+      <c r="N35" s="77">
         <f>+AA35-SUM(K35:M35)</f>
         <v>0</v>
       </c>
-      <c r="O35" s="78">
+      <c r="O35" s="77">
         <v>0</v>
       </c>
-      <c r="P35" s="78"/>
-      <c r="Q35" s="78"/>
-      <c r="R35" s="78"/>
+      <c r="P35" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="77"/>
+      <c r="R35" s="77"/>
       <c r="S35" s="21"/>
       <c r="T35" s="21">
         <v>0</v>
@@ -4061,16 +4112,19 @@
         <f>2359-SUM(K36:L36)</f>
         <v>817</v>
       </c>
-      <c r="N36" s="78">
+      <c r="N36" s="77">
         <f>+AA36-SUM(K36:M36)</f>
         <v>911</v>
       </c>
-      <c r="O36" s="78">
+      <c r="O36" s="77">
         <v>812</v>
       </c>
-      <c r="P36" s="78"/>
-      <c r="Q36" s="78"/>
-      <c r="R36" s="78"/>
+      <c r="P36" s="77">
+        <f>1670-O36</f>
+        <v>858</v>
+      </c>
+      <c r="Q36" s="77"/>
+      <c r="R36" s="77"/>
       <c r="S36" s="21"/>
       <c r="T36" s="21">
         <v>1100</v>
@@ -4140,7 +4194,7 @@
         <v>1882</v>
       </c>
       <c r="K37" s="21">
-        <f t="shared" ref="K37:O37" si="22">K34+K35-K36</f>
+        <f t="shared" ref="K37:P37" si="22">K34+K35-K36</f>
         <v>1642</v>
       </c>
       <c r="L37" s="21">
@@ -4159,7 +4213,10 @@
         <f t="shared" si="22"/>
         <v>1756</v>
       </c>
-      <c r="P37" s="21"/>
+      <c r="P37" s="21">
+        <f t="shared" si="22"/>
+        <v>2087</v>
+      </c>
       <c r="Q37" s="21"/>
       <c r="R37" s="21"/>
       <c r="S37" s="21"/>
@@ -4243,16 +4300,19 @@
         <f>-49-SUM(K38:L38)</f>
         <v>-37</v>
       </c>
-      <c r="N38" s="78">
+      <c r="N38" s="77">
         <f>+AA38-SUM(K38:M38)</f>
         <v>-31</v>
       </c>
-      <c r="O38" s="78">
+      <c r="O38" s="77">
         <v>-16</v>
       </c>
-      <c r="P38" s="78"/>
-      <c r="Q38" s="78"/>
-      <c r="R38" s="78"/>
+      <c r="P38" s="77">
+        <f>-51-O38</f>
+        <v>-35</v>
+      </c>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="77"/>
       <c r="S38" s="21"/>
       <c r="T38" s="21">
         <v>17</v>
@@ -4326,16 +4386,19 @@
         <f>69-SUM(K39:L39)</f>
         <v>27</v>
       </c>
-      <c r="N39" s="78">
+      <c r="N39" s="77">
         <f>+AA39-SUM(K39:M39)</f>
         <v>33</v>
       </c>
-      <c r="O39" s="85">
+      <c r="O39" s="80">
         <v>23</v>
       </c>
-      <c r="P39" s="78"/>
-      <c r="Q39" s="78"/>
-      <c r="R39" s="78"/>
+      <c r="P39" s="77">
+        <f>52-O39</f>
+        <v>29</v>
+      </c>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
       <c r="S39" s="21"/>
       <c r="T39" s="21">
         <v>54</v>
@@ -4405,7 +4468,7 @@
         <v>1824</v>
       </c>
       <c r="K40" s="21">
-        <f t="shared" ref="K40:O40" si="25">K37+K38+K39</f>
+        <f t="shared" ref="K40:P40" si="25">K37+K38+K39</f>
         <v>1672</v>
       </c>
       <c r="L40" s="21">
@@ -4424,7 +4487,10 @@
         <f t="shared" si="25"/>
         <v>1763</v>
       </c>
-      <c r="P40" s="21"/>
+      <c r="P40" s="21">
+        <f t="shared" si="25"/>
+        <v>2081</v>
+      </c>
       <c r="Q40" s="21"/>
       <c r="R40" s="21"/>
       <c r="S40" s="21"/>
@@ -4506,16 +4572,19 @@
         <f>1341-SUM(K41:L41)</f>
         <v>531</v>
       </c>
-      <c r="N41" s="78">
+      <c r="N41" s="77">
         <f>+AA41-SUM(K41:M41)</f>
         <v>459</v>
       </c>
-      <c r="O41" s="78">
+      <c r="O41" s="77">
         <v>388</v>
       </c>
-      <c r="P41" s="78"/>
-      <c r="Q41" s="78"/>
-      <c r="R41" s="78"/>
+      <c r="P41" s="77">
+        <f>865-O41</f>
+        <v>477</v>
+      </c>
+      <c r="Q41" s="77"/>
+      <c r="R41" s="77"/>
       <c r="S41" s="21"/>
       <c r="T41" s="21">
         <v>980</v>
@@ -4585,7 +4654,7 @@
         <v>1418</v>
       </c>
       <c r="K42" s="21">
-        <f t="shared" ref="K42:O42" si="28">K40-K41</f>
+        <f t="shared" ref="K42:P42" si="28">K40-K41</f>
         <v>1306</v>
       </c>
       <c r="L42" s="21">
@@ -4604,7 +4673,10 @@
         <f t="shared" si="28"/>
         <v>1375</v>
       </c>
-      <c r="P42" s="21"/>
+      <c r="P42" s="21">
+        <f t="shared" si="28"/>
+        <v>1604</v>
+      </c>
       <c r="Q42" s="21"/>
       <c r="R42" s="21"/>
       <c r="S42" s="21"/>
@@ -4684,16 +4756,18 @@
       <c r="M43" s="21">
         <v>0</v>
       </c>
-      <c r="N43" s="78">
+      <c r="N43" s="77">
         <f>+AA43-SUM(K43:M43)</f>
         <v>0</v>
       </c>
-      <c r="O43" s="78">
+      <c r="O43" s="77">
         <v>0</v>
       </c>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="78"/>
-      <c r="R43" s="78"/>
+      <c r="P43" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="77"/>
       <c r="S43" s="21"/>
       <c r="T43" s="21">
         <v>4</v>
@@ -4763,7 +4837,7 @@
         <v>1418</v>
       </c>
       <c r="K44" s="21">
-        <f t="shared" ref="K44:O44" si="31">K42-K43</f>
+        <f t="shared" ref="K44:P44" si="31">K42-K43</f>
         <v>1306</v>
       </c>
       <c r="L44" s="21">
@@ -4782,7 +4856,10 @@
         <f t="shared" si="31"/>
         <v>1375</v>
       </c>
-      <c r="P44" s="21"/>
+      <c r="P44" s="21">
+        <f t="shared" si="31"/>
+        <v>1604</v>
+      </c>
       <c r="Q44" s="21"/>
       <c r="R44" s="21"/>
       <c r="S44" s="21"/>
@@ -4903,7 +4980,7 @@
         <v>0.47692228260726244</v>
       </c>
       <c r="M46" s="3">
-        <f t="shared" ref="M46:O46" si="34">M44/M47</f>
+        <f t="shared" ref="M46:P46" si="34">M44/M47</f>
         <v>0.58729164123314104</v>
       </c>
       <c r="N46" s="3">
@@ -4914,6 +4991,10 @@
         <f t="shared" si="34"/>
         <v>0.44125450349761663</v>
       </c>
+      <c r="P46" s="3">
+        <f t="shared" si="34"/>
+        <v>0.5147754781125764</v>
+      </c>
       <c r="T46" s="3">
         <f>T44/T47</f>
         <v>1.1060789241132536</v>
@@ -4991,7 +5072,9 @@
       <c r="O47" s="5">
         <v>3116.1155050000002</v>
       </c>
-      <c r="P47" s="5"/>
+      <c r="P47" s="5">
+        <v>3115.9215389999999</v>
+      </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
@@ -5254,39 +5337,48 @@
         <f t="shared" si="37"/>
         <v>4.8840440312065914E-2</v>
       </c>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
+      <c r="N55" s="30">
+        <f t="shared" ref="N55" si="38">N29/J29-1</f>
+        <v>4.3086529884032165E-2</v>
+      </c>
+      <c r="O55" s="30">
+        <f t="shared" ref="O55" si="39">O29/K29-1</f>
+        <v>5.7529610829103239E-2</v>
+      </c>
+      <c r="P55" s="30">
+        <f t="shared" ref="P55" si="40">P29/L29-1</f>
+        <v>9.144103937320236E-2</v>
+      </c>
       <c r="Q55" s="30"/>
       <c r="R55" s="30"/>
       <c r="S55" s="27"/>
       <c r="T55" s="27"/>
       <c r="U55" s="30">
-        <f t="shared" ref="U55:AA55" si="38">U29/T29-1</f>
+        <f t="shared" ref="U55:AA55" si="41">U29/T29-1</f>
         <v>8.192771084337358E-2</v>
       </c>
       <c r="V55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>-0.27874995581008943</v>
       </c>
       <c r="W55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.3584942652681109</v>
       </c>
       <c r="X55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.17509741665463996</v>
       </c>
       <c r="Y55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.10371825969480186</v>
       </c>
       <c r="Z55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>7.4693298467187752E-2</v>
       </c>
       <c r="AA55" s="30">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>3.1890660592255093E-2</v>
       </c>
     </row>
@@ -5295,84 +5387,93 @@
         <v>62</v>
       </c>
       <c r="C56" s="29">
-        <f t="shared" ref="C56:J56" si="39">C31/C29</f>
+        <f t="shared" ref="C56:J56" si="42">C31/C29</f>
         <v>0.60478255157009586</v>
       </c>
       <c r="D56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.56250676480138539</v>
       </c>
       <c r="E56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.61680749029458781</v>
       </c>
       <c r="F56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.53762816792416324</v>
       </c>
       <c r="G56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.60613496932515343</v>
       </c>
       <c r="H56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.56490166414523446</v>
       </c>
       <c r="I56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.61440632681414986</v>
       </c>
       <c r="J56" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.53996431757359498</v>
       </c>
       <c r="K56" s="29">
-        <f t="shared" ref="K56:L56" si="40">K31/K29</f>
+        <f t="shared" ref="K56:L56" si="43">K31/K29</f>
         <v>0.60575296108291032</v>
       </c>
       <c r="L56" s="29">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.56441535257363884</v>
       </c>
       <c r="M56" s="29">
-        <f t="shared" ref="M56" si="41">M31/M29</f>
+        <f t="shared" ref="M56:P56" si="44">M31/M29</f>
         <v>0.62227430201752598</v>
       </c>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
+      <c r="N56" s="29">
+        <f t="shared" si="44"/>
+        <v>0.54836226802360388</v>
+      </c>
+      <c r="O56" s="29">
+        <f t="shared" si="44"/>
+        <v>0.61245714285714281</v>
+      </c>
+      <c r="P56" s="29">
+        <f t="shared" si="44"/>
+        <v>0.56674238982280778</v>
+      </c>
       <c r="Q56" s="29"/>
       <c r="R56" s="29"/>
       <c r="T56" s="29">
-        <f t="shared" ref="T56:Z56" si="42">T31/T29</f>
+        <f t="shared" ref="T56:Z56" si="45">T31/T29</f>
         <v>0.56668579078217629</v>
       </c>
       <c r="U56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.55884328490119139</v>
       </c>
       <c r="V56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.55822958533477107</v>
       </c>
       <c r="W56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.57057295425025256</v>
       </c>
       <c r="X56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.56980564340323625</v>
       </c>
       <c r="Y56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.57754471861351431</v>
       </c>
       <c r="Z56" s="29">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>0.57838061710499067</v>
       </c>
       <c r="AA56" s="29">
-        <f t="shared" ref="AA56" si="43">AA31/AA29</f>
+        <f t="shared" ref="AA56" si="46">AA31/AA29</f>
         <v>0.58253060405378287</v>
       </c>
     </row>
@@ -5381,84 +5482,93 @@
         <v>63</v>
       </c>
       <c r="C57" s="29">
-        <f t="shared" ref="C57:J57" si="44">C34/C29</f>
+        <f t="shared" ref="C57:J57" si="47">C34/C29</f>
         <v>0.28839837077913544</v>
       </c>
       <c r="D57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.26702024028574523</v>
       </c>
       <c r="E57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.3158255309431377</v>
       </c>
       <c r="F57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.23408783130199265</v>
       </c>
       <c r="G57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.29079754601226993</v>
       </c>
       <c r="H57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.2692889561270802</v>
       </c>
       <c r="I57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.31270706422998823</v>
       </c>
       <c r="J57" s="29">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.24638715432649419</v>
       </c>
       <c r="K57" s="29">
-        <f t="shared" ref="K57:L57" si="45">K34/K29</f>
+        <f t="shared" ref="K57:L57" si="48">K34/K29</f>
         <v>0.28934010152284262</v>
       </c>
       <c r="L57" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0.26976098383417635</v>
       </c>
       <c r="M57" s="29">
-        <f t="shared" ref="M57" si="46">M34/M29</f>
+        <f t="shared" ref="M57:P57" si="49">M34/M29</f>
         <v>0.32484206235989405</v>
       </c>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
+      <c r="N57" s="29">
+        <f t="shared" si="49"/>
+        <v>0.25357051227229965</v>
+      </c>
+      <c r="O57" s="29">
+        <f t="shared" si="49"/>
+        <v>0.29348571428571429</v>
+      </c>
+      <c r="P57" s="29">
+        <f t="shared" si="49"/>
+        <v>0.26760563380281688</v>
+      </c>
       <c r="Q57" s="29"/>
       <c r="R57" s="29"/>
       <c r="T57" s="29">
-        <f t="shared" ref="T57:Z57" si="47">T34/T29</f>
+        <f t="shared" ref="T57:Z57" si="50">T34/T29</f>
         <v>0.20872059667240389</v>
       </c>
       <c r="U57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.26863930427404814</v>
       </c>
       <c r="V57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.22306636604254484</v>
       </c>
       <c r="W57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.25916438158464422</v>
       </c>
       <c r="X57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.26552857011268383</v>
       </c>
       <c r="Y57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.27398670264556152</v>
       </c>
       <c r="Z57" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.27772313108303998</v>
       </c>
       <c r="AA57" s="29">
-        <f t="shared" ref="AA57" si="48">AA34/AA29</f>
+        <f t="shared" ref="AA57" si="51">AA34/AA29</f>
         <v>0.28263596227172388</v>
       </c>
     </row>
@@ -5467,84 +5577,93 @@
         <v>64</v>
       </c>
       <c r="C58" s="29">
-        <f t="shared" ref="C58:J58" si="49">C37/C29</f>
+        <f t="shared" ref="C58:J58" si="52">C37/C29</f>
         <v>0.194849559847589</v>
       </c>
       <c r="D58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.18194609806256087</v>
       </c>
       <c r="E58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.23144553551039049</v>
       </c>
       <c r="F58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.1563165022248017</v>
       </c>
       <c r="G58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.2007361963190184</v>
       </c>
       <c r="H58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.19213313161875945</v>
       </c>
       <c r="I58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.22785080688254783</v>
       </c>
       <c r="J58" s="29">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.16788581623550403</v>
       </c>
       <c r="K58" s="29">
-        <f t="shared" ref="K58:L58" si="50">K37/K29</f>
+        <f t="shared" ref="K58:L58" si="53">K37/K29</f>
         <v>0.1984529852550157</v>
       </c>
       <c r="L58" s="29">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0.19141128632351484</v>
       </c>
       <c r="M58" s="29">
-        <f t="shared" ref="M58" si="51">M37/M29</f>
+        <f t="shared" ref="M58:P58" si="54">M37/M29</f>
         <v>0.24159364173629508</v>
       </c>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
+      <c r="N58" s="29">
+        <f t="shared" si="54"/>
+        <v>0.17566065167194048</v>
+      </c>
+      <c r="O58" s="29">
+        <f t="shared" si="54"/>
+        <v>0.20068571428571427</v>
+      </c>
+      <c r="P58" s="29">
+        <f t="shared" si="54"/>
+        <v>0.18964107223989096</v>
+      </c>
       <c r="Q58" s="29"/>
       <c r="R58" s="29"/>
       <c r="T58" s="29">
-        <f t="shared" ref="T58:Z58" si="52">T37/T29</f>
+        <f t="shared" ref="T58:Z58" si="55">T37/T29</f>
         <v>0.16664754255115702</v>
       </c>
       <c r="U58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.16873475448085692</v>
       </c>
       <c r="V58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>7.3816292520341137E-2</v>
       </c>
       <c r="W58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.15449559821041997</v>
       </c>
       <c r="X58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.16942491326107648</v>
       </c>
       <c r="Y58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.18938993518235181</v>
       </c>
       <c r="Z58" s="29">
-        <f t="shared" si="52"/>
+        <f t="shared" si="55"/>
         <v>0.1955632636156554</v>
       </c>
       <c r="AA58" s="29">
-        <f t="shared" ref="AA58" si="53">AA37/AA29</f>
+        <f t="shared" ref="AA58" si="56">AA37/AA29</f>
         <v>0.20060706401766004</v>
       </c>
     </row>
@@ -5553,84 +5672,93 @@
         <v>65</v>
       </c>
       <c r="C59" s="29">
-        <f t="shared" ref="C59:J59" si="54">C42/C29</f>
+        <f t="shared" ref="C59:J59" si="57">C42/C29</f>
         <v>0.15398764945473656</v>
       </c>
       <c r="D59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.14590323628098278</v>
       </c>
       <c r="E59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.18189084265814112</v>
       </c>
       <c r="F59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.12381505126716967</v>
       </c>
       <c r="G59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.15926380368098159</v>
       </c>
       <c r="H59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.14916792738275339</v>
       </c>
       <c r="I59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.17975846959495564</v>
       </c>
       <c r="J59" s="29">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0.12649420160570918</v>
       </c>
       <c r="K59" s="29">
-        <f t="shared" ref="K59:L59" si="55">K42/K29</f>
+        <f t="shared" ref="K59:L59" si="58">K42/K29</f>
         <v>0.15784384819917816</v>
       </c>
       <c r="L59" s="29">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.14737677278587721</v>
       </c>
       <c r="M59" s="29">
-        <f t="shared" ref="M59" si="56">M42/M29</f>
+        <f t="shared" ref="M59:P59" si="59">M42/M29</f>
         <v>0.18646831057672714</v>
       </c>
-      <c r="N59" s="29"/>
-      <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
+      <c r="N59" s="29">
+        <f t="shared" si="59"/>
+        <v>0.13657743949371418</v>
+      </c>
+      <c r="O59" s="29">
+        <f t="shared" si="59"/>
+        <v>0.15714285714285714</v>
+      </c>
+      <c r="P59" s="29">
+        <f t="shared" si="59"/>
+        <v>0.14575193094048161</v>
+      </c>
       <c r="Q59" s="29"/>
       <c r="R59" s="29"/>
       <c r="T59" s="29">
-        <f t="shared" ref="T59:Z59" si="57">T42/T29</f>
+        <f t="shared" ref="T59:Z59" si="60">T42/T29</f>
         <v>0.13187990055459936</v>
       </c>
       <c r="U59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.12896383497719802</v>
       </c>
       <c r="V59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>5.4063327124791685E-2</v>
       </c>
       <c r="W59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.11722470775003609</v>
       </c>
       <c r="X59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.12729896527372656</v>
       </c>
       <c r="Y59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.15005424652961305</v>
       </c>
       <c r="Z59" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.15212776972458067</v>
       </c>
       <c r="AA59" s="29">
-        <f t="shared" ref="AA59" si="58">AA42/AA29</f>
+        <f t="shared" ref="AA59" si="61">AA42/AA29</f>
         <v>0.15600541842263696</v>
       </c>
     </row>
@@ -5659,31 +5787,31 @@
       <c r="R60" s="29"/>
       <c r="T60" s="29"/>
       <c r="U60" s="29">
-        <f t="shared" ref="U60:AA60" si="59">(U34-T34)/(U29-T29)</f>
+        <f t="shared" ref="U60:AA60" si="62">(U34-T34)/(U29-T29)</f>
         <v>1</v>
       </c>
       <c r="V60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.38655675332910588</v>
       </c>
       <c r="W60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.35985780694558384</v>
       </c>
       <c r="X60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.30187512878631773</v>
       </c>
       <c r="Y60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.35553582001184131</v>
       </c>
       <c r="Z60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.32774674115456237</v>
       </c>
       <c r="AA60" s="29">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.43668831168831168</v>
       </c>
     </row>
@@ -5692,84 +5820,93 @@
         <v>66</v>
       </c>
       <c r="C61" s="29">
-        <f t="shared" ref="C61:M61" si="60">C41/C40</f>
+        <f t="shared" ref="C61:M61" si="63">C41/C40</f>
         <v>0.22126245847176079</v>
       </c>
       <c r="D61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.22839152833428736</v>
       </c>
       <c r="E61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.19748110831234256</v>
       </c>
       <c r="F61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.21520539546290618</v>
       </c>
       <c r="G61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.2232196289646918</v>
       </c>
       <c r="H61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.23248572911261028</v>
       </c>
       <c r="I61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.21985157699443414</v>
       </c>
       <c r="J61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.22258771929824561</v>
       </c>
       <c r="K61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.21889952153110048</v>
       </c>
       <c r="L61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.23005181347150258</v>
       </c>
       <c r="M61" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.22490470139771285</v>
       </c>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
+      <c r="N61" s="29">
+        <f t="shared" ref="N61:P61" si="64">N41/N40</f>
+        <v>0.2232490272373541</v>
+      </c>
+      <c r="O61" s="29">
+        <f t="shared" si="64"/>
+        <v>0.22007941009642654</v>
+      </c>
+      <c r="P61" s="29">
+        <f t="shared" si="64"/>
+        <v>0.22921672272945698</v>
+      </c>
       <c r="Q61" s="29"/>
       <c r="R61" s="29"/>
       <c r="T61" s="29">
-        <f t="shared" ref="T61:Z61" si="61">T41/T40</f>
+        <f t="shared" ref="T61:Z61" si="65">T41/T40</f>
         <v>0.22131887985546522</v>
       </c>
       <c r="U61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.22084579239641178</v>
       </c>
       <c r="V61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.21214285714285713</v>
       </c>
       <c r="W61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.22606002858504048</v>
       </c>
       <c r="X61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.22605936158297554</v>
       </c>
       <c r="Y61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.21473285776677828</v>
       </c>
       <c r="Z61" s="29">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>0.22436320443447275</v>
       </c>
       <c r="AA61" s="29">
-        <f t="shared" ref="AA61" si="62">AA41/AA40</f>
+        <f t="shared" ref="AA61" si="66">AA41/AA40</f>
         <v>0.22446689113355781</v>
       </c>
     </row>
@@ -6113,35 +6250,35 @@
         <v>44</v>
       </c>
       <c r="C68" s="21">
-        <f t="shared" ref="C68:J68" si="63">SUM(C63:C67)</f>
+        <f t="shared" ref="C68:J68" si="67">SUM(C63:C67)</f>
         <v>0</v>
       </c>
       <c r="D68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="E68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>16891</v>
       </c>
       <c r="H68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="I68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>17992</v>
       </c>
       <c r="J68" s="21">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="K68" s="21"/>
@@ -6154,35 +6291,35 @@
       <c r="R68" s="21"/>
       <c r="S68" s="21"/>
       <c r="T68" s="21">
-        <f t="shared" ref="T68:AA68" si="64">SUM(T63:T67)</f>
+        <f t="shared" ref="T68:AA68" si="68">SUM(T63:T67)</f>
         <v>11064</v>
       </c>
       <c r="U68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>16978</v>
       </c>
       <c r="V68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>15461</v>
       </c>
       <c r="W68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>15343</v>
       </c>
       <c r="X68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>15344</v>
       </c>
       <c r="Y68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>16719</v>
       </c>
       <c r="Z68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>18357</v>
       </c>
       <c r="AA68" s="21">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>19947</v>
       </c>
       <c r="AB68" s="21"/>
@@ -6543,35 +6680,35 @@
         <v>50</v>
       </c>
       <c r="C74" s="21">
-        <f t="shared" ref="C74:J74" si="65">SUM(C69:C73)</f>
+        <f t="shared" ref="C74:J74" si="69">SUM(C69:C73)</f>
         <v>0</v>
       </c>
       <c r="D74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="E74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="F74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="G74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>17079</v>
       </c>
       <c r="H74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="I74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>18099</v>
       </c>
       <c r="J74" s="21">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="K74" s="21"/>
@@ -6584,23 +6721,23 @@
       <c r="R74" s="21"/>
       <c r="S74" s="21"/>
       <c r="T74" s="21">
-        <f t="shared" ref="T74:X74" si="66">SUM(T69:T73)</f>
+        <f t="shared" ref="T74:X74" si="70">SUM(T69:T73)</f>
         <v>10620</v>
       </c>
       <c r="U74" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>11413</v>
       </c>
       <c r="V74" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>10957</v>
       </c>
       <c r="W74" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>13602</v>
       </c>
       <c r="X74" s="21">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>14640</v>
       </c>
       <c r="Y74" s="21">
@@ -6638,35 +6775,35 @@
         <v>49</v>
       </c>
       <c r="C75" s="28">
-        <f t="shared" ref="C75:J75" si="67">C68+C74</f>
+        <f t="shared" ref="C75:J75" si="71">C68+C74</f>
         <v>0</v>
       </c>
       <c r="D75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="E75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="F75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="G75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>33970</v>
       </c>
       <c r="H75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="I75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>36091</v>
       </c>
       <c r="J75" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="K75" s="28"/>
@@ -6679,35 +6816,35 @@
       <c r="R75" s="28"/>
       <c r="S75" s="28"/>
       <c r="T75" s="28">
-        <f t="shared" ref="T75:AA75" si="68">T68+T74</f>
+        <f t="shared" ref="T75:AA75" si="72">T68+T74</f>
         <v>21684</v>
       </c>
       <c r="U75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>28391</v>
       </c>
       <c r="V75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>26418</v>
       </c>
       <c r="W75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>28945</v>
       </c>
       <c r="X75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>29984</v>
       </c>
       <c r="Y75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>32735</v>
       </c>
       <c r="Z75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>34713</v>
       </c>
       <c r="AA75" s="28">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>35638</v>
       </c>
       <c r="AB75" s="21"/>
@@ -6912,35 +7049,35 @@
         <v>53</v>
       </c>
       <c r="C79" s="28">
-        <f t="shared" ref="C79:J79" si="69">C77+C78</f>
+        <f t="shared" ref="C79:J79" si="73">C77+C78</f>
         <v>0</v>
       </c>
       <c r="D79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="E79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="F79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="G79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>17554</v>
       </c>
       <c r="H79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="I79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>18140</v>
       </c>
       <c r="J79" s="28">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="K79" s="28"/>
@@ -6953,23 +7090,23 @@
       <c r="R79" s="28"/>
       <c r="S79" s="28"/>
       <c r="T79" s="28">
-        <f t="shared" ref="T79:X79" si="70">T77+T78</f>
+        <f t="shared" ref="T79:X79" si="74">T77+T78</f>
         <v>14683</v>
       </c>
       <c r="U79" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>14949</v>
       </c>
       <c r="V79" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>14550</v>
       </c>
       <c r="W79" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>15759</v>
       </c>
       <c r="X79" s="28">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>17033</v>
       </c>
       <c r="Y79" s="28">
@@ -7275,35 +7412,35 @@
         <v>57</v>
       </c>
       <c r="C84" s="21">
-        <f t="shared" ref="C84:J84" si="71">SUM(C80:C83)</f>
+        <f t="shared" ref="C84:J84" si="75">SUM(C80:C83)</f>
         <v>0</v>
       </c>
       <c r="D84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="E84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="F84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="G84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4804</v>
       </c>
       <c r="H84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="I84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>4999</v>
       </c>
       <c r="J84" s="21">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="K84" s="21"/>
@@ -7316,23 +7453,23 @@
       <c r="R84" s="21"/>
       <c r="S84" s="21"/>
       <c r="T84" s="21">
-        <f t="shared" ref="T84:X84" si="72">SUM(T80:T83)</f>
+        <f t="shared" ref="T84:X84" si="76">SUM(T80:T83)</f>
         <v>1618</v>
       </c>
       <c r="U84" s="21">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>6136</v>
       </c>
       <c r="V84" s="21">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>5530</v>
       </c>
       <c r="W84" s="21">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>5158</v>
       </c>
       <c r="X84" s="21">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>4813</v>
       </c>
       <c r="Y84" s="21">
@@ -7638,35 +7775,35 @@
         <v>59</v>
       </c>
       <c r="C89" s="21">
-        <f t="shared" ref="C89:J89" si="73">SUM(C85:C88)</f>
+        <f t="shared" ref="C89:J89" si="77">SUM(C85:C88)</f>
         <v>0</v>
       </c>
       <c r="D89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="E89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="F89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="G89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>11612</v>
       </c>
       <c r="H89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="I89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>12952</v>
       </c>
       <c r="J89" s="21">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="K89" s="21"/>
@@ -7679,23 +7816,23 @@
       <c r="R89" s="21"/>
       <c r="S89" s="21"/>
       <c r="T89" s="21">
-        <f t="shared" ref="T89:X89" si="74">SUM(T85:T88)</f>
+        <f t="shared" ref="T89:X89" si="78">SUM(T85:T88)</f>
         <v>5382</v>
       </c>
       <c r="U89" s="21">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>7306</v>
       </c>
       <c r="V89" s="21">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>6337</v>
       </c>
       <c r="W89" s="21">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>8030</v>
       </c>
       <c r="X89" s="21">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>8137</v>
       </c>
       <c r="Y89" s="21">
@@ -7733,35 +7870,35 @@
         <v>60</v>
       </c>
       <c r="C90" s="28">
-        <f t="shared" ref="C90:J90" si="75">C79+C84+C89</f>
+        <f t="shared" ref="C90:J90" si="79">C79+C84+C89</f>
         <v>0</v>
       </c>
       <c r="D90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="E90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="F90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="G90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>33970</v>
       </c>
       <c r="H90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="I90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>36091</v>
       </c>
       <c r="J90" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="K90" s="28"/>
@@ -7774,35 +7911,35 @@
       <c r="R90" s="28"/>
       <c r="S90" s="28"/>
       <c r="T90" s="28">
-        <f t="shared" ref="T90:AA90" si="76">T79+T84+T89</f>
+        <f t="shared" ref="T90:AA90" si="80">T79+T84+T89</f>
         <v>21683</v>
       </c>
       <c r="U90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>28391</v>
       </c>
       <c r="V90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>26417</v>
       </c>
       <c r="W90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>28947</v>
       </c>
       <c r="X90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>29983</v>
       </c>
       <c r="Y90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>32736</v>
       </c>
       <c r="Z90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>34714</v>
       </c>
       <c r="AA90" s="28">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>35637</v>
       </c>
       <c r="AB90" s="21"/>
@@ -7935,31 +8072,31 @@
       <c r="R93" s="21"/>
       <c r="S93" s="21"/>
       <c r="T93" s="21">
-        <f t="shared" ref="T93:Z93" si="77">T40</f>
+        <f t="shared" ref="T93:Z93" si="81">T40</f>
         <v>4428</v>
       </c>
       <c r="U93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>4682</v>
       </c>
       <c r="V93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>1400</v>
       </c>
       <c r="W93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>4198</v>
       </c>
       <c r="X93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>5357</v>
       </c>
       <c r="Y93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>6869</v>
       </c>
       <c r="Z93" s="21">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>7577</v>
       </c>
       <c r="AA93" s="21">
@@ -8513,19 +8650,19 @@
       <c r="R102" s="21"/>
       <c r="S102" s="21"/>
       <c r="T102" s="21">
-        <f t="shared" ref="T102:W102" si="78">SUM(T99:T101)</f>
+        <f t="shared" ref="T102:W102" si="82">SUM(T99:T101)</f>
         <v>-349</v>
       </c>
       <c r="U102" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>205</v>
       </c>
       <c r="V102" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>-847</v>
       </c>
       <c r="W102" s="21">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>223</v>
       </c>
       <c r="X102" s="21">
@@ -8586,23 +8723,23 @@
       <c r="R103" s="28"/>
       <c r="S103" s="28"/>
       <c r="T103" s="28">
-        <f t="shared" ref="T103:X103" si="79">T93+SUM(T94:T97)+T102</f>
+        <f t="shared" ref="T103:X103" si="83">T93+SUM(T94:T97)+T102</f>
         <v>4028</v>
       </c>
       <c r="U103" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>6901</v>
       </c>
       <c r="V103" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>3016</v>
       </c>
       <c r="W103" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>6754</v>
       </c>
       <c r="X103" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>6673</v>
       </c>
       <c r="Y103" s="28">
@@ -8989,23 +9126,23 @@
       <c r="R109" s="28"/>
       <c r="S109" s="28"/>
       <c r="T109" s="28">
-        <f t="shared" ref="T109:X109" si="80">SUM(T104:T108)</f>
+        <f t="shared" ref="T109:X109" si="84">SUM(T104:T108)</f>
         <v>-1875</v>
       </c>
       <c r="U109" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>-2376</v>
       </c>
       <c r="V109" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>2514</v>
       </c>
       <c r="W109" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>-3253</v>
       </c>
       <c r="X109" s="28">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>-3503</v>
       </c>
       <c r="Y109" s="28">
@@ -9387,23 +9524,23 @@
       <c r="R115" s="28"/>
       <c r="S115" s="28"/>
       <c r="T115" s="28">
-        <f t="shared" ref="T115:X115" si="81">SUM(T110:T114)</f>
+        <f t="shared" ref="T115:X115" si="85">SUM(T110:T114)</f>
         <v>-2260</v>
       </c>
       <c r="U115" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-4629</v>
       </c>
       <c r="V115" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-2786</v>
       </c>
       <c r="W115" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-3909</v>
       </c>
       <c r="X115" s="28">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-4614</v>
       </c>
       <c r="Y115" s="28">
@@ -9572,23 +9709,23 @@
       <c r="R118" s="28"/>
       <c r="S118" s="28"/>
       <c r="T118" s="28">
-        <f t="shared" ref="T118:X118" si="82">T103+T109+T115+T116</f>
+        <f t="shared" ref="T118:X118" si="86">T103+T109+T115+T116</f>
         <v>-66</v>
       </c>
       <c r="U118" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>-84</v>
       </c>
       <c r="V118" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>2617</v>
       </c>
       <c r="W118" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>-377</v>
       </c>
       <c r="X118" s="28">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>-1461</v>
       </c>
       <c r="Y118" s="28">
@@ -10443,7 +10580,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="K2" s="77" t="s">
+      <c r="K2" s="76" t="s">
         <v>203</v>
       </c>
       <c r="M2" s="6" t="s">
@@ -11573,7 +11710,7 @@
       </c>
       <c r="J3" s="38">
         <f>Main!J3</f>
-        <v>55</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -11588,7 +11725,7 @@
       </c>
       <c r="J4" s="40">
         <f ca="1">V60</f>
-        <v>69.112929806708422</v>
+        <v>68.989180079178112</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
@@ -11603,7 +11740,7 @@
       </c>
       <c r="J5" s="41">
         <f ca="1">J4/J3-1</f>
-        <v>0.25659872375833492</v>
+        <v>0.25777903517188894</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
@@ -13292,7 +13429,7 @@
       <c r="Q56" s="3"/>
       <c r="V56" s="3">
         <f>Main!J6</f>
-        <v>10797</v>
+        <v>10399</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
@@ -13320,7 +13457,7 @@
       <c r="U57" s="68"/>
       <c r="V57" s="68">
         <f>Main!J7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
@@ -13333,7 +13470,7 @@
       <c r="Q58" s="3"/>
       <c r="V58" s="3">
         <f ca="1">V55+V56-V57</f>
-        <v>215363.87216666079</v>
+        <v>214964.87216666079</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
@@ -13361,7 +13498,7 @@
       <c r="U59" s="68"/>
       <c r="V59" s="68">
         <f>Main!J4</f>
-        <v>3116.1155050000002</v>
+        <v>3115.9215389999999</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
@@ -13370,7 +13507,7 @@
       </c>
       <c r="V60" s="34">
         <f ca="1">V58/V59</f>
-        <v>69.112929806708422</v>
+        <v>68.989180079178112</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
@@ -13403,19 +13540,19 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="70"/>
-      <c r="C66" s="80" t="s">
+      <c r="C66" s="83" t="s">
         <v>163</v>
       </c>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="80"/>
-      <c r="J66" s="81"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="83"/>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="83"/>
+      <c r="J66" s="84"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B67" s="82" t="s">
+      <c r="B67" s="85" t="s">
         <v>162</v>
       </c>
       <c r="C67" s="71"/>
@@ -13428,7 +13565,7 @@
       <c r="J67" s="72"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="82"/>
+      <c r="B68" s="85"/>
       <c r="C68" s="73"/>
       <c r="D68" s="35"/>
       <c r="E68" s="35"/>
@@ -13439,7 +13576,7 @@
       <c r="J68" s="35"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="82"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="73"/>
       <c r="D69" s="35"/>
       <c r="E69" s="35"/>
@@ -13450,7 +13587,7 @@
       <c r="J69" s="35"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="82"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="73"/>
       <c r="D70" s="35"/>
       <c r="E70" s="35"/>
@@ -13461,7 +13598,7 @@
       <c r="J70" s="35"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B71" s="82"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="73"/>
       <c r="D71" s="35"/>
       <c r="E71" s="35"/>
@@ -13472,7 +13609,7 @@
       <c r="J71" s="35"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B72" s="82"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="73"/>
       <c r="D72" s="35"/>
       <c r="E72" s="35"/>
@@ -13483,7 +13620,7 @@
       <c r="J72" s="35"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B73" s="82"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="73"/>
       <c r="D73" s="35"/>
       <c r="E73" s="35"/>
@@ -13494,7 +13631,7 @@
       <c r="J73" s="35"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B74" s="83"/>
+      <c r="B74" s="86"/>
       <c r="C74" s="73"/>
       <c r="D74" s="35"/>
       <c r="E74" s="35"/>
